--- a/tables/Table 3 Model coefficients.xlsx
+++ b/tables/Table 3 Model coefficients.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\OSM_red_squirrel_distribution\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D373D7A-A15D-4906-AC1E-4CF62CAE2DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E587ACE-94BE-4A5F-A4C1-66C858CC37D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>Site [nested]</t>
   </si>
   <si>
-    <t>Array</t>
-  </si>
-  <si>
     <t>Fixed effects</t>
   </si>
   <si>
@@ -70,10 +67,13 @@
     <t>Modeled scale (m)</t>
   </si>
   <si>
-    <t>Cumulative Disturbance</t>
-  </si>
-  <si>
-    <t>Edge Density × Cumulative Disturbance</t>
+    <t>Cumulative Footprint</t>
+  </si>
+  <si>
+    <t>Edge Density × Cumulative Footprint</t>
+  </si>
+  <si>
+    <t>Landscape Unit</t>
   </si>
 </sst>
 </file>
@@ -492,22 +492,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.44140625" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="2.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="8" max="8" width="2.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -517,14 +517,14 @@
       <c r="G1" s="3"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>0</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
@@ -551,11 +551,11 @@
         <v>0.249</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
@@ -575,7 +575,7 @@
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
@@ -591,11 +591,11 @@
         <v>0.13400000000000001</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
@@ -615,7 +615,7 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
@@ -635,7 +635,7 @@
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
@@ -655,11 +655,11 @@
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="11">
         <v>2000</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="13">
         <v>2000</v>
@@ -695,7 +695,7 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
@@ -705,21 +705,21 @@
       <c r="G11" s="7"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>12</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>13</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
@@ -733,11 +733,11 @@
       <c r="G13" s="6"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D14" s="9">
         <v>0.69850614888001195</v>
@@ -747,7 +747,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
